--- a/experiments/results/abp/cplex-cp-abp.xlsx
+++ b/experiments/results/abp/cplex-cp-abp.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x0.75" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1.25" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1.5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="abp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="abp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="abp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="abp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="abp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="abp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,66 +419,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -540,17 +535,20 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -602,17 +600,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -664,17 +665,20 @@
           <t>17</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -726,17 +730,20 @@
           <t>21</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -788,17 +795,20 @@
           <t>21</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -850,17 +860,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -912,17 +925,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -974,17 +990,20 @@
           <t>29</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>28</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>47.76</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1036,17 +1055,20 @@
           <t>35</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>34</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>315.8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1094,17 +1116,20 @@
           <t>42</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>41</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>249.4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1152,17 +1177,20 @@
           <t>51</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>50</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1214,17 +1242,20 @@
           <t>58</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>57</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1276,17 +1307,20 @@
           <t>190</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>189</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>140.8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1334,17 +1368,20 @@
           <t>190</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>189</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>142.3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1392,17 +1429,20 @@
           <t>181</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>180</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>129.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>708.04</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1454,17 +1494,20 @@
           <t>203</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>202</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>131.7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1512,17 +1555,20 @@
           <t>227</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>226</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>27.33</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1574,17 +1620,20 @@
           <t>218</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>217</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>203.0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1632,17 +1681,20 @@
           <t>260</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>259</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>122.5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>265.93</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1694,17 +1746,20 @@
           <t>255</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>254</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>183.5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1752,17 +1807,20 @@
           <t>331</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>330</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>105.8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>22.83</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1814,17 +1872,20 @@
           <t>329</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>328</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>205.1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1872,17 +1933,20 @@
           <t>341</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>340</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>202.4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1930,17 +1994,20 @@
           <t>309</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>308</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>237.2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1800.09</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1953,66 +2020,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2041,40 +2113,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2103,40 +2178,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2165,40 +2243,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2227,40 +2308,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>20</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2289,40 +2373,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2351,40 +2438,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2413,40 +2503,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2475,40 +2568,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>28</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>149.11</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>79.29</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2537,40 +2633,47 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>220.6</t>
-        </is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>33</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2595,40 +2698,47 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>146.6</t>
-        </is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>34</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2653,40 +2763,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>50</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2715,40 +2828,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>12.8</t>
-        </is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>57</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2777,40 +2893,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>176.7</t>
-        </is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>187</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>110.6</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2835,40 +2954,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>176.4</t>
-        </is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>187</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>109.9</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2893,40 +3015,47 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>197.2</t>
-        </is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>180</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>35.7</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2951,40 +3080,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>180</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>115.1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3009,40 +3141,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>227</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>116.1</t>
-        </is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>226</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>118.05</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3071,40 +3206,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>211.3</t>
-        </is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>217</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>158.8</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3129,40 +3267,47 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>180.8</t>
-        </is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>130</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.07</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3187,40 +3332,47 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>239.9</t>
-        </is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>168</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>61.6</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>12.23</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3245,40 +3397,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>331</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>134.8</t>
-        </is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>330</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>65.39</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3307,40 +3462,47 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>240.3</t>
-        </is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>164</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3365,40 +3527,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>251.5</t>
-        </is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>340</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>167.3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3423,40 +3588,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>285.9</t>
-        </is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>290</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.11</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>182.4</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3469,66 +3637,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3557,40 +3730,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3619,40 +3795,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>18</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3681,40 +3860,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3743,40 +3925,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3805,40 +3990,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3867,40 +4055,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>36</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3929,40 +4120,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3991,40 +4185,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>236.0</t>
-        </is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>962.01</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>149.11</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4053,44 +4250,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>220.6</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4115,44 +4311,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>68</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>146.6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4177,40 +4372,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>76</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4239,40 +4437,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>87</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4301,40 +4502,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>148.1</t>
-        </is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>307</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>176.7</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4359,40 +4563,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>149.1</t>
-        </is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>307</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>176.4</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4417,44 +4624,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>251</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>292</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>197.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4479,40 +4685,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>188.0</t>
-        </is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>307</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4537,40 +4746,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>341</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>340</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>116.1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>118.05</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4599,40 +4811,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>344.5</t>
-        </is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>366</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>211.3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4657,44 +4872,45 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>390</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>180.8</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.07</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4719,44 +4935,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>69.9</t>
-        </is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>399</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>239.9</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4781,40 +4996,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>496</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>495</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>65.39</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4843,44 +5061,45 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>240.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4905,40 +5124,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>257.6</t>
-        </is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>510</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>251.5</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4963,40 +5185,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>239.0</t>
-        </is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>469</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>285.9</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.11</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5009,66 +5234,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5097,40 +5327,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5159,40 +5392,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>18</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5221,40 +5457,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5283,40 +5522,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5345,40 +5587,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5407,40 +5652,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>36</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5469,40 +5717,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5531,40 +5782,47 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>250.77</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5589,40 +5847,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>51</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5651,40 +5912,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>52</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5713,40 +5977,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>76</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5775,40 +6042,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>87</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5837,40 +6107,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>171.5</t>
-        </is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>275</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>128.3</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.07</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5895,40 +6168,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>172.7</t>
-        </is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>275</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>127.6</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.05</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5953,40 +6229,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>271</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>270</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6015,40 +6294,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>147</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>204.3</t>
-        </is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>268</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6073,40 +6355,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>341</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>340</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6135,40 +6420,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>278.0</t>
-        </is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>329</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>186.6</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6193,40 +6481,43 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>195</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6255,40 +6546,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>253</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>252</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>20.50</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6317,40 +6611,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>496</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>495</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>32.52</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6379,40 +6676,43 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>247</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>64.2</t>
-        </is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>246</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>48.4</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6441,40 +6741,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>268.3</t>
-        </is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>510</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>200.3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6499,40 +6802,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>177</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>268.9</t>
-        </is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>435</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>232.9</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6545,66 +6851,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -6633,40 +6944,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>18</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6695,40 +7009,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>27</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6757,40 +7074,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>34</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6819,40 +7139,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>45</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6881,40 +7204,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>42</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6943,40 +7269,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>52</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7005,40 +7334,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>52</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7067,40 +7399,47 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>432.2</t>
-        </is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>56</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>236.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>962.01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7125,40 +7464,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>69</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7187,40 +7529,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>70</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7249,40 +7594,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>102</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7311,40 +7659,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>117</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7373,40 +7724,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>172.7</t>
-        </is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>374</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>148.1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7431,40 +7785,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>173.9</t>
-        </is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>374</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.05</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>149.1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7489,40 +7846,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>361</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>360</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7551,40 +7911,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>216.5</t>
-        </is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>360</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>188.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7609,40 +7972,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>455</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>454</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7671,40 +8037,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>312.3</t>
-        </is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>441</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.05</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>344.5</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7729,40 +8098,43 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>546</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>262</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>261</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7791,40 +8163,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>340</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>110.2</t>
-        </is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>339</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>9.58</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7853,40 +8228,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>220</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>662</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>661</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>660</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>85.65</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>14.45</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7915,40 +8293,43 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>330</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>71.8</t>
-        </is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>329</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7977,40 +8358,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>299</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>297.9</t>
-        </is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>680</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>257.6</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8035,6 +8419,3232 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>580</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>239.0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Time limit (s)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best bound</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Best objective</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Time consumed (s)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>52</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>64</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>64</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>70</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>84</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>86</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>126</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>144</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>462</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>171.5</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>462</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>172.7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>450</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>448</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>204.3</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>566</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>38.8</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>546</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>278.0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>326</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>48.5</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>423</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>55.65</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>825</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>58.47</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>411</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>64.2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>850</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>268.3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>725</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>268.9</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Time limit (s)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best bound</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Best objective</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Time consumed (s)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>65</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>62</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>76</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>76</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>84</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>432.2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>102</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>104</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>152</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>174</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>561</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>172.7</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>561</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>173.9</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.05</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>540</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>47.7</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>540</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>216.5</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>680</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>658</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>312.3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.05</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>391</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>507</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>110.2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>80.36</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>990</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>115.9</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>85.65</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>493</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1020</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>297.9</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
@@ -8058,17 +11668,20 @@
           <t>871</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>870</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>340.7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/experiments/results/abp/cplex-cp-abp.xlsx
+++ b/experiments/results/abp/cplex-cp-abp.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="abp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="abp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="abp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="abp_x1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="abp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="abp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x0.5_no_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x0.75_no_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,67 +435,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -527,25 +539,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -605,12 +617,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -670,12 +682,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -735,12 +747,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -800,12 +812,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -865,12 +877,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -930,12 +942,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -995,12 +1007,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>79.29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1052,23 +1064,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>315.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1113,23 +1129,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>249.4</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1182,12 +1202,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1247,12 +1267,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1304,20 +1324,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>188</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>110.6</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1365,20 +1385,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>188</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>109.9</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1434,12 +1454,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>708.04</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1486,25 +1506,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>181</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>115.1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1560,12 +1580,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1612,7 +1632,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1625,7 +1645,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>158.8</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1673,25 +1693,25 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>131</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>259</v>
+        <v>130</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>265.93</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1738,28 +1758,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>169</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>183.5</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>12.23</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1812,12 +1836,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>105.8</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>14.93</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1864,28 +1888,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>328</v>
+        <v>164</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>205.1</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1925,7 +1953,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1938,7 +1966,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>202.4</t>
+          <t>167.3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1986,25 +2014,25 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>237.2</t>
+          <t>182.4</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2024,67 +2052,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2128,25 +2156,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2206,12 +2234,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2271,12 +2299,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2336,12 +2364,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2401,12 +2429,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2466,12 +2494,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2531,12 +2559,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2596,12 +2624,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>79.29</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2653,27 +2681,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>315.8</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2718,27 +2742,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>249.4</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2791,12 +2811,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2856,12 +2876,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2913,20 +2933,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>110.6</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2974,20 +2994,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>109.9</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -3043,12 +3063,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>708.04</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3095,25 +3115,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>115.1</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -3169,12 +3189,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3221,7 +3241,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3234,7 +3254,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>158.8</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3282,25 +3302,25 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>130</v>
+        <v>259</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>265.93</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3347,32 +3367,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>168</v>
+        <v>254</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12.23</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3425,12 +3441,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>105.8</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3477,32 +3493,28 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>328</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>205.1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3542,7 +3554,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3555,7 +3567,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>167.3</t>
+          <t>202.4</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3603,25 +3615,25 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>309</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>182.4</t>
+          <t>237.2</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3641,67 +3653,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3745,25 +3757,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -3823,12 +3835,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3888,12 +3900,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3953,12 +3965,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4018,12 +4030,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4083,7 +4095,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -4148,12 +4160,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4213,12 +4225,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>149.11</t>
+          <t>250.77</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4270,23 +4282,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>220.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4326,28 +4342,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>146.6</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4400,12 +4420,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4465,12 +4485,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -4522,20 +4542,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>176.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -4583,20 +4603,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>276</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>176.4</t>
+          <t>127.6</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.05</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -4639,28 +4659,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>271</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>197.2</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4700,25 +4724,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>147</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -4774,12 +4798,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>116.1</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>118.05</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -4831,20 +4855,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>366</v>
+        <v>329</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>211.3</t>
+          <t>186.6</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800.01</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -4887,30 +4911,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>195</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>180.8</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1800.07</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4950,28 +4976,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>253</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>399</v>
+        <v>252</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>239.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>20.50</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5024,12 +5054,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>134.8</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.39</t>
+          <t>32.52</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -5076,30 +5106,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>247</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>246</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>240.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5139,7 +5171,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5152,12 +5184,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>200.3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -5200,25 +5232,25 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>177</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>285.9</t>
+          <t>232.9</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1800.11</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -5238,67 +5270,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5342,25 +5374,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -5420,12 +5452,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5485,12 +5517,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5550,12 +5582,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -5615,12 +5647,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5680,7 +5712,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -5745,12 +5777,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5810,12 +5842,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>250.77</t>
+          <t>149.11</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5867,27 +5899,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>220.6</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5927,32 +5955,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>146.6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6005,12 +6029,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -6070,12 +6094,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6127,20 +6151,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>176.7</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -6188,20 +6212,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>176.4</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1800.05</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -6244,32 +6268,28 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>251</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>197.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6309,25 +6329,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>139</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -6383,12 +6403,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>116.1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>118.05</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -6440,20 +6460,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>367</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>186.6</t>
+          <t>211.3</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -6496,32 +6516,30 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>390</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>195</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>180.8</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.07</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6561,32 +6579,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>252</v>
+        <v>399</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>239.9</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>20.50</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6639,12 +6653,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>65.39</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -6691,32 +6705,30 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>246</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>240.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6756,7 +6768,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6769,12 +6781,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>200.3</t>
+          <t>251.5</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -6817,25 +6829,25 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>232.9</t>
+          <t>285.9</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.11</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -6855,67 +6867,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -8472,67 +8484,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -10085,67 +10097,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>

--- a/experiments/results/abp/cplex-cp-abp.xlsx
+++ b/experiments/results/abp/cplex-cp-abp.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="abp_x1_no_hole" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11698,4 +11699,1599 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time limit (s)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Best bound</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best objective</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Time consumed (s)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>34.20</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>27.9</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>143.20</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>219.7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>46</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>343.49</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>281.4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>53</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>107.70</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>54</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>229.6</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>56</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>211.1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1565.90</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>186.5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>117</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>200.7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>282.2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>279.5</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.05</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>209.5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>245.2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>217.4</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1800.12</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>551</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>281.3</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>661</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>215.6</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>834.81</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>262.1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1800.19</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>680</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>437.3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.15</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>679</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>355.8</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.20</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>